--- a/Result/checksun_type/不鏽鋼棒線.xlsx
+++ b/Result/checksun_type/不鏽鋼棒線.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>31.65</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>32.62</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>34.35</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34.35</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>88619.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>56397.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>56397</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>81909.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>71062.74</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>71062.74000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-6411.908493448966</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>88619</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>88619.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>31.41</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>32.66</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>34.41</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>34.41</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>30296.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>55604.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>55604.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>81238.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>75154.3</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>75154.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9133.301158309303</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>30296</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>30296.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>31.37</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>34.54</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>34.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>51673.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>67354.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>67354.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>87056.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>76625.64</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>76625.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-6445.922781027301</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>51673</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>51673.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>31.34</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>32.94</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>34.65</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>32.94</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>34.65</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>47092.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>74374.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>74374.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>92061.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>76543.48</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>76543.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-4666.992142730625</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>47092</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>47092.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>31.32</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.13</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>34.77</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>64305.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>91626.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>91626</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>98215.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>76798.64</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>76798.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1468.16294006641</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>64305</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>64305.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>31.49</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.35</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>34.89</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>34.89</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>84657.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>107421.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>107421.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>104305.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>77733.42</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>77733.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1309.777454456271</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>84657</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>84657.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>31.89</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.58</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>35.03</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>35.03</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>89047.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>106873.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>106873</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>107795.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>80213.18</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>80213.17999999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>3050.914537543809</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>89047</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>89047.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.83</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>35.15</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>35.15</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>86773.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>106758.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>106758.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>107839.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>79632.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>79632.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>4958.934851327998</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>86773</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>86773.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>32.75</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>34.07</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>35.27</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>35.27</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>133348.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>109748.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>109748</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>110112.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>80021.1</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>80021.10000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>7751.216197757982</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>133348</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>133348.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>33.23</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>35.38</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>35.38</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>143284.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>104805.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>104805.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>105668.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>79834.04</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>79834.03999999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>6473.181828452303</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>143284</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>143284.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>33.52</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>34.47</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>35.5</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>35.5</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>81913.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>101188.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>101188.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>97048.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>81169.24</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>81169.24000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>3351.661949856643</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>81913</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>81913.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>19.69</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>17.01</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>13.06</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>13.06</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1030.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>2356.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>2356</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>2480.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>915.86</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>915.86</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>119.6203873874458</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1030</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1030.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>20.04</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>12.87</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>12.87</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>580.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3385.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>3385.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2584.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>942.8</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>942.8</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>245.8964964244842</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>580</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>580.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>20.87</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>16.11</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>12.72</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>12.72</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1513.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>3764.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>3764.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2563.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>948.5</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>948.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>465.7232058908075</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1513</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1513.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>21.44</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>15.68</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>12.57</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>12.57</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>3277.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3810.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>3810</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2487.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>936.3</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>936.3</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>663.1641049180262</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>3277</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>3277.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>21.61</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>12.41</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>12.41</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>5380.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3492.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>3492.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>2168.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>875.2</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>875.2</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>732.5380997812654</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>5380</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>5380.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>22.02</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>14.69</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>12.23</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>6177.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>2605.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>2605.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1666.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>777.32</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>777.3200000000001</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>580.1603031651334</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>6177</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>6177.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>22.41</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>12.02</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>2477.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1783.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1783.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1153.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>667.98</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>667.98</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>256.3648686004763</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>2477</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2477.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>23.03</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>13.46</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>11.78</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>11.78</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1739.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1361.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1361.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>988.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>628.3</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>628.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>181.0726453438062</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1739</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1739.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>20.67</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>12.85</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>11.57</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>11.57</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>1690.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1164.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1164.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>880.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>599.74</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>599.74</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>146.1168747862846</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1690</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1690.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>18.56</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>11.4</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>946.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>844.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>844.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>769.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>568.28</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>568.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>96.21159989031503</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>946</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>946.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>16.08</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>11.72</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>11.19</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>11.19</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>2064.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>726.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>726.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>730.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>554.88</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>554.88</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>101.1965071857043</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>2064</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>2064.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>11.87</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>12.25</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>12.82</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>12.82</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>12.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>632.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>632.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-63.86270100726495</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>12</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>11.78</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>12.29</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>12.86</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>12.86</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>2943.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1196.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1196.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>30.15100202381109</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>2943</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>2943.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>11.76</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>12.89</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>12.89</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>12.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>613.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>613.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-150.6562437183595</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>12</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>11.84</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>12.41</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>12.93</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>12.93</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>47.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>635.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>635.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-89.53601464580458</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>47</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>11.92</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>12.47</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>12.97</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>12.97</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>147.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1225.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1225.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-2.773686876233114</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>147</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>12.05</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>12.54</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>13</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>2834.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>0</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>110.5572701830199</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>2834</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>2834.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>12.24</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>12.62</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>13.05</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>0</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-19.38269366744066</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>26</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>12.36</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>12.69</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>13.08</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>13.08</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>122.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>0</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>96.53816846288169</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>122</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>12.4</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>12.74</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>13.12</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>13.12</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>2998.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>0</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>248.4058940610964</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>2998</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>2998.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>12.44</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>12.78</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>13.15</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>0</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>36.62824808959294</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>0</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>12.42</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>13.18</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>13.18</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>0</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>36.62824808959294</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>0</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>25.02</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>25.32</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>331.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>485.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>485.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>640.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>757.72</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>757.72</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-41.27741637364784</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>331</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>331.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>26.04</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>26.04</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>681.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>648.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>648</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>630.6</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>756.16</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>756.16</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-22.43691546251989</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>681</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>681.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>25.05</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>25.38</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>26.09</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>26.09</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>499.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>581.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>581.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>622.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>757.3</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>757.3</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-32.22059575153276</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>499</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>499.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>25.09</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>25.41</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>26.15</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>456.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>600.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>600.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>638.6</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>760.92</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>760.92</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-25.54654631613914</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>456</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>456.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>25.19</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>26.21</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>26.21</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>459.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>743.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>743.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>694.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>756.98</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>756.98</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-10.49267046857199</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>459</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>459.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>25.28</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>25.46</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>26.28</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>26.28</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1145.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>795.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>795.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>704.6</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>761.76</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>761.76</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>11.06617611611568</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1145</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1145.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>25.38</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>26.33</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>26.33</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>347.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>613.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>613.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>624.1</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>754.88</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>754.88</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-32.03069219562019</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>347</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>347.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>25.33</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>26.38</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>26.38</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>597.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>663.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>663.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>647.3</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>753.46</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>753.46</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-6.953693633970602</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>597</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>597.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>25.33</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>25.59</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>26.42</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>26.42</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>1168.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>676.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>676.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>613.5</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>754.24</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>754.24</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>2.333221941027773</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>1168</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1168.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>25.28</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>26.46</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>721.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>645.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>645.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>589.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>737.22</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>737.22</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-45.66165659258274</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>721</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>721.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>25.21</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>25.66</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>26.51</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>26.51</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>233.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>613.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>613.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>555.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>742.34</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>742.34</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-64.70213819086268</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>233</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>233.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>20.02</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>19.78</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>19.94</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>19.94</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>26219629.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>16889576.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>16889576</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>17236189.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>20277790.28</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>20277790.28</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-302881.9023336619</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>26219629</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>26219629.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>19.89</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>19.73</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>19.94</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>19.94</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>17532722.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>14859100.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>14859100</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>16642108.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>20371841.18</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>20371841.18</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-1128834.726736229</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>17532722</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>17532722.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>19.84</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>19.95</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>11740057.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>16014559.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>16014559.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>16278001.2</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>20292426.12</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>20292426.12</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-1337711.771356456</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>11740057</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>11740057.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>19.82</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>19.96</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>19.96</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>18789662.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>18102005.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>18102005</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>17635266.7</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>20278770.0</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>20278770</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-967689.4504083358</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>18789662</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>18789662.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>19.89</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>19.97</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>19.97</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>10165810.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>17346115.8</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>17346115.8</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>24061820.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>20181907.52</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>20181907.52</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-1159840.618682154</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>10165810</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>10165810.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>19.94</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>19.97</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>19.97</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>16067249.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>17582802.6</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>17582802.6</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>24285645.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>20299032.42</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>20299032.42</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-468935.2655489594</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>16067249</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>16067249.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>20.06</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>19.99</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>23310018.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>18425116.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>18425116.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>24110880.8</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>20453854.52</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>20453854.52</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-97476.96587479487</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>23310018</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>23310018.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>20.1</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>20</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>22177286.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>16541443.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>16541443.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>23454311.7</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>20348159.38</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>20348159.38</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-339351.8961304575</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>22177286</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>22177286.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>20.13</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>20</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>15010216.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>17168528.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>17168528.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>22516228.9</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>20143353.8</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>20143353.8</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-551403.6573481709</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>15010216</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>15010216.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>20.17</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>19.57</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>20.01</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>20.01</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>11349244.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>30777524.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>30777524.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>22335947.5</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>20370385.8</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>20370385.8</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-66741.39989675581</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>11349244</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>11349244.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>20.05</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>19.55</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>20.02</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>20278820.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>30988489.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>30988489</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>22686745.2</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>20671912.34</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>20671912.34</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>1020263.875030149</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>20278820</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>20278820.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>28.99</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>30.08</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>28.2</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>1203482068.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>1387618376.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>1387618376.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>4264040487.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>3111629550.18</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>3111629550.18</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-488176249.5318046</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>1203482068</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>1203482068.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>29.02</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>30.16</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>28.07</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>28.07</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>942023312.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1584381817.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1584381817</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>4484329546.0</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>3097694126.7</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>3097694126.7</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-425650424.2230182</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>942023312</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>942023312.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>29.25</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>30.24</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>27.94</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>27.94</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>1007778782.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>2139497377.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>2139497377.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>4665494634.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>3096337448.26</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>3096337448.26</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-293112577.631073</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>1007778782</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>1007778782.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>29.73</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>30.32</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>27.81</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>27.81</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1607084998.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>3258049059.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>3258049059.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>4688553902.3</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>3083594155.06</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>3083594155.06</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-100349719.3700418</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1607084998</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1607084998.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>30.62</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>30.38</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>27.69</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>27.69</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>2177722724.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>5262265961.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>5262265961.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>4687463430.7</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>3075231109.06</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>3075231109.06</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>114398330.6946478</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>2177722724</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>31.58</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>30.41</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>27.56</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>2187299269.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>7140462597.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>7140462597.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>4678699401.4</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>3064464439.28</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>3064464439.28</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>355955848.3336811</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>2187299269</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>2187299269.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>32.04</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>30.44</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>27.46</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>27.46</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>3717601115.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>7384277275.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>7384277275</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>4600886187.9</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>3041422265.56</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>3041422265.56</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>687299249.1275253</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>3717601115</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>3717601115.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>32.03</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>30.45</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>27.29</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>27.29</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>6600537191.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>7191491890.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>7191491890.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>4454153458.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2973288757.28</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2973288757.28</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>972139650.7213211</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>6600537191</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>6600537191.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>31.7</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>30.34</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>27.1</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>11628169508.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>6119058745.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>6119058745.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>3965899981.1</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2847760321.4</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2847760321.4</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>1035449228.758123</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>11628169508</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>11628169508.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>31.07</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>30.19</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>26.9</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>26.9</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>11568705906.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>4112660900.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>4112660900</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>2972243250.2</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2623033685.92</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2623033685.92</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>550236262.3907671</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>11568705906</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>11568705906.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>30.27</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>29.82</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>26.66</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>26.66</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>3406372655.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>2216936205.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>2216936205</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>2119863690.1</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2406749639.6</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2406749639.6</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-156205313.0051274</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>3406372655</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>3406372655.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
